--- a/Employee_Reports_wi48/Kasansula Francis Kiwanuka Q0527.xlsx
+++ b/Employee_Reports_wi48/Kasansula Francis Kiwanuka Q0527.xlsx
@@ -454,13 +454,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1206,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-125</v>
+        <v>-128</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1304,11 +1304,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-122</v>
+        <v>-125</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1327,9 +1327,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
           <t>25-Mar-2025</t>
@@ -1341,11 +1353,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-110</v>
+        <v>-113</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1361,36 +1373,85 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
+          <t>Matar LOTO Procedure (SOPs)</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>MATAR</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>FM-DE-24-SOP-SA-013</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>01-Jul-2026</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>01-Jul-2027</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
           <t>IS0 55001 (Other Trainings)</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>06-Jul-2025</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>06-Jul-2027</t>
         </is>
       </c>
-      <c r="H20" s="3" t="n">
-        <v>358</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="H21" s="3" t="n">
+        <v>355</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
